--- a/data/dividends_info_20260929.xlsx
+++ b/data/dividends_info_20260929.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47.77000045776367</v>
+        <v>47.03499984741211</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1884027614351279</v>
+        <v>0.1913468699733648</v>
       </c>
       <c r="J2" t="n">
         <v>167</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.55000305175781</v>
+        <v>63.95000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.084430622627117</v>
+        <v>1.094605147222557</v>
       </c>
       <c r="J3" t="n">
         <v>146</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47.79999923706055</v>
+        <v>47.03499984741211</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1882845218336755</v>
+        <v>0.1913468699733648</v>
       </c>
       <c r="J6" t="n">
         <v>76</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.065000057220459</v>
+        <v>2.069999933242798</v>
       </c>
       <c r="I7" t="n">
-        <v>3.728813455997861</v>
+        <v>3.719806883248261</v>
       </c>
       <c r="J7" t="n">
         <v>55</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>50.29999923706055</v>
+        <v>50.40000152587891</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6163021962266652</v>
+        <v>0.6150793464576071</v>
       </c>
       <c r="J8" t="n">
         <v>55</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.125</v>
+        <v>24.29000091552734</v>
       </c>
       <c r="I9" t="n">
-        <v>1.119170984455959</v>
+        <v>1.111568504830327</v>
       </c>
       <c r="J9" t="n">
         <v>55</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>24.26000022888184</v>
+        <v>24.29999923706055</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4319867866184</v>
+        <v>2.427983615325287</v>
       </c>
       <c r="J10" t="n">
         <v>55</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>13</v>
+        <v>12.89999961853027</v>
       </c>
       <c r="I11" t="n">
-        <v>1.615384615384615</v>
+        <v>1.627907024883507</v>
       </c>
       <c r="J11" t="n">
         <v>48</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.880000114440918</v>
+        <v>5.869999885559082</v>
       </c>
       <c r="I12" t="n">
-        <v>3.401360478017889</v>
+        <v>3.407155091979209</v>
       </c>
       <c r="J12" t="n">
         <v>48</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.199999809265137</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I13" t="n">
-        <v>1.129032292797713</v>
+        <v>1.147541001547219</v>
       </c>
       <c r="J13" t="n">
         <v>41</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.63000011444092</v>
+        <v>10.5600004196167</v>
       </c>
       <c r="I15" t="n">
-        <v>4.327375306187318</v>
+        <v>4.356060432966316</v>
       </c>
       <c r="J15" t="n">
         <v>27</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.099999904632568</v>
+        <v>5.139999866485596</v>
       </c>
       <c r="I18" t="n">
-        <v>0.980392175195585</v>
+        <v>0.972762671182457</v>
       </c>
       <c r="J18" t="n">
         <v>6</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.25</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="I19" t="n">
-        <v>3.04</v>
+        <v>0.5000000062741732</v>
       </c>
       <c r="J19" t="n">
         <v>-1</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>24.1200008392334</v>
+        <v>24.29000091552734</v>
       </c>
       <c r="I20" t="n">
-        <v>1.119402946126023</v>
+        <v>1.111568504830327</v>
       </c>
       <c r="J20" t="n">
         <v>-8</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.919000029563904</v>
+        <v>1.89900004863739</v>
       </c>
       <c r="I21" t="n">
-        <v>2.9702969839429</v>
+        <v>3.001579701954185</v>
       </c>
       <c r="J21" t="n">
         <v>-8</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>47.79999923706055</v>
+        <v>47.03499984741211</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1882845218336755</v>
+        <v>0.1913468699733648</v>
       </c>
       <c r="J22" t="n">
         <v>-8</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>5.050505001853162</v>
       </c>
       <c r="J24" t="n">
         <v>-15</v>
@@ -2096,7 +2096,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2130,7 +2130,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2419,7 +2419,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2436,7 +2436,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2453,7 +2453,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2470,7 +2470,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2504,7 +2504,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2538,7 +2538,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2555,7 +2555,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ETI S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2572,7 +2572,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>ETI S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2589,7 +2589,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2606,7 +2606,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2633,14 +2633,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2650,14 +2650,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2674,7 +2674,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2708,7 +2708,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2725,7 +2725,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2735,14 +2735,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2759,7 +2759,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2776,7 +2776,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>OPT S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2912,7 +2912,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2929,7 +2929,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2939,14 +2939,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2963,7 +2963,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2980,7 +2980,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2997,7 +2997,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3014,7 +3014,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3031,7 +3031,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3048,7 +3048,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3065,7 +3065,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3082,7 +3082,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OPT S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3099,7 +3099,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3109,14 +3109,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3133,7 +3133,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3150,7 +3150,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3160,14 +3160,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3184,7 +3184,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3201,7 +3201,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3218,7 +3218,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3235,7 +3235,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3252,7 +3252,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3269,7 +3269,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3303,7 +3303,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3313,14 +3313,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3337,7 +3337,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3354,7 +3354,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3371,7 +3371,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3388,7 +3388,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3422,7 +3422,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3439,7 +3439,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3456,7 +3456,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3473,7 +3473,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3490,7 +3490,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3507,7 +3507,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3524,7 +3524,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3558,7 +3558,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3575,7 +3575,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3592,7 +3592,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3602,14 +3602,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3626,7 +3626,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Alia Mentis S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3643,7 +3643,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3660,7 +3660,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3677,7 +3677,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3694,7 +3694,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3711,7 +3711,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3728,7 +3728,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>First Point S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3745,7 +3745,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3762,7 +3762,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3779,7 +3779,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3796,7 +3796,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3813,7 +3813,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Alia Mentis S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3847,7 +3847,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3864,7 +3864,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3881,7 +3881,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3898,7 +3898,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3908,14 +3908,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3932,7 +3932,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3942,14 +3942,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SB Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>LANDI RENZO S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3959,14 +3959,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3983,7 +3983,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3993,14 +3993,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>SB Annual Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4017,7 +4017,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4061,14 +4061,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4078,14 +4078,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4095,14 +4095,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4112,14 +4112,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4136,7 +4136,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4146,14 +4146,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4163,14 +4163,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4180,14 +4180,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4197,14 +4197,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4214,14 +4214,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4231,14 +4231,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -4333,14 +4333,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4357,7 +4357,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4374,7 +4374,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4384,14 +4384,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4401,14 +4401,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4418,14 +4418,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4469,14 +4469,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4486,14 +4486,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4612,7 +4612,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4622,14 +4622,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4663,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4673,14 +4673,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4690,14 +4690,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4714,7 +4714,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4731,7 +4731,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4748,7 +4748,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>LANDI RENZO S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4765,7 +4765,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4775,14 +4775,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -4850,7 +4850,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4860,14 +4860,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4877,14 +4877,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4894,14 +4894,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4911,14 +4911,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4928,14 +4928,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4945,14 +4945,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4962,14 +4962,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4979,14 +4979,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4996,14 +4996,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5013,14 +5013,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5030,14 +5030,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5054,7 +5054,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5088,7 +5088,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5098,14 +5098,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5122,7 +5122,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5132,14 +5132,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5149,14 +5149,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5166,14 +5166,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5183,14 +5183,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5207,7 +5207,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5224,7 +5224,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5241,7 +5241,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5258,7 +5258,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5275,7 +5275,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5292,7 +5292,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5302,14 +5302,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5326,7 +5326,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5351,146 +5351,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0005439861</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-11-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6.199999809265137</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1.129032292797713</v>
-      </c>
-      <c r="I2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0000076502</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-11-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>50.29999923706055</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0.6163021962266652</v>
-      </c>
-      <c r="I3" t="n">
-        <v>55</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5501,401 +5364,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AMPLIFON S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AMPLIFON S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Cogefeed S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DHH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>EDISON S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ELICA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Estrima S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>FOPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Haiki+ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>INNOVATEC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Italgas S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Italgas S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>KME Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>S.S. Lazio S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Seri Industrial S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>VINEXT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>